--- a/Result/profitability/2851.xlsx
+++ b/Result/profitability/2851.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.85375</v>
+        <v>1.51875</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -778,7 +778,7 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.85875</v>
+        <v>1.495</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -895,7 +895,7 @@
         <v>-0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.75625</v>
+        <v>1.36</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -1012,7 +1012,7 @@
         <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6987499999999999</v>
+        <v>1.37125</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1129,7 +1129,7 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7062499999999999</v>
+        <v>1.285</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1254,7 +1254,7 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.635</v>
+        <v>1.1275</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1379,7 +1379,7 @@
         <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4625</v>
+        <v>0.8762500000000002</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9800,6 +9800,119 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>5124</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>151.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5126</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4489</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.5475</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.439130434782609</v>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>23.39130434782609</v>
+      </c>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="n">
+        <v>2.475660639777468</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
